--- a/forms/trg/Formulir_TRG_dgrg.xlsx
+++ b/forms/trg/Formulir_TRG_dgrg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B27)</f>
+        <f>COUNTA(Anggota!B5:B28)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F27)</f>
+        <f>COUNTA(Anggota!F5:F28)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,22 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Ambo Ako, M.Sc., IPU</t>
+          <t>Dr. Agr. Ir. Renny Fatmyah Utamy, S. Pt., M. Agr., IPM</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Tatalaksana Ladang Ternak Perah</t>
+          <t>Department of Animal Production, Faculty of Animal Science, Hasanuddin University</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Management of Dairy Farm Operations</t>
+          <t>Manajemen Pakan Ternak Perah (Feed Management of Dairy Cows)</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,13 +937,13 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-8291-9560</t>
+          <t>0000-0002-7908-6710</t>
         </is>
       </c>
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>55977837800</t>
+          <t>55744037500</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -958,22 +958,22 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Muhammad Ihsan Andi Dagong, S. Pt., M. Si</t>
+          <t>Prof. Dr. Ir. Ambo Ako, M.Sc., IPU</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Animal Breeding and Molecular Genetic</t>
+          <t>Tatalaksana Ladang Ternak Perah</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Management of Dairy Farm Operations</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -982,13 +982,13 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-5060-2614%20</t>
+          <t>0000-0001-8291-9560</t>
         </is>
       </c>
       <c r="K6" s="12" t="n"/>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57190659880</t>
+          <t>55977837800</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Zyahrul Ramadan, S. Pt., M. Si</t>
+          <t>Prof. Dr. Muhammad Ihsan Andi Dagong, S. Pt., M. Si</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Nutrition and Physiology in Dairy Science</t>
+          <t>Animal Breeding and Molecular Genetic</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -1027,13 +1027,13 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0009-0009-7460-103X</t>
+          <t>0000-0001-5060-2614%20</t>
         </is>
       </c>
       <c r="K7" s="12" t="n"/>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>59161668100</t>
+          <t>57190659880</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1048,22 +1048,22 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Mamat Hamidi Kamalludin</t>
+          <t>Zyahrul Ramadan, S. Pt., M. Si</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Animal Genetics and Breeding</t>
+          <t>Nutrition and Physiology in Dairy Science</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Universiti Putra Malaysia</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1072,13 +1072,13 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-9728-8212</t>
+          <t>0009-0009-7460-103X</t>
         </is>
       </c>
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>56440088200</t>
+          <t>59161668100</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1093,17 +1093,17 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr. Aimi Nabilah Hussein</t>
+          <t>Dr. Mamat Hamidi Kamalludin</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>ANIMAL BEHAVIOUR &amp; DAIRY PRODUCTION</t>
+          <t>Animal Genetics and Breeding</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -1117,13 +1117,13 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-7481-9682</t>
+          <t>0000-0001-9728-8212</t>
         </is>
       </c>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>57192988602</t>
+          <t>56440088200</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1138,31 +1138,39 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. Md. Nazmul Haque</t>
+          <t>Dr. Aimi Nabilah Hussein</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Animal Breeding &amp; Genetics</t>
+          <t>ANIMAL BEHAVIOUR &amp; DAIRY PRODUCTION</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Bangladesh Agricultural University</t>
+          <t>Universiti Putra Malaysia</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
-      <c r="J10" s="12" t="n"/>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-7481-9682</t>
+        </is>
+      </c>
       <c r="K10" s="12" t="n"/>
-      <c r="L10" s="12" t="n"/>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
+          <t>57192988602</t>
+        </is>
+      </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1175,39 +1183,31 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Rara Mufliha, S.Pt., M.Si</t>
+          <t>Dr. Md. Nazmul Haque</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Dairy Science</t>
+          <t>Animal Breeding &amp; Genetics</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Laboratory of Dairy Cow, Faculty of Animal Science, Hasanuddin University Makassar, South Sulawesi, Indonesia</t>
+          <t>Bangladesh Agricultural University</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>0009-0007-1878-6629</t>
-        </is>
-      </c>
+      <c r="J11" s="12" t="n"/>
       <c r="K11" s="12" t="n"/>
-      <c r="L11" s="11" t="inlineStr">
-        <is>
-          <t>59161668000</t>
-        </is>
-      </c>
+      <c r="L11" s="12" t="n"/>
       <c r="M11" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1220,22 +1220,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Viterah Niode, S.Pt</t>
+          <t>Rara Mufliha, S.Pt., M.Si</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Physiology Dairy Goat</t>
+          <t>Dairy Science</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Laboratory of Dairy Cow, Faculty of Animal Science, Hasanuddin University Makassar, South Sulawesi, Indonesia</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1244,11 +1244,15 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>0009-0000-3291-0621</t>
+          <t>0009-0007-1878-6629</t>
         </is>
       </c>
       <c r="K12" s="12" t="n"/>
-      <c r="L12" s="12" t="n"/>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
+          <t>59161668000</t>
+        </is>
+      </c>
       <c r="M12" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1261,17 +1265,17 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Azisah Nurfadillah, S.Pt</t>
+          <t>Viterah Niode, S.Pt</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Dairy Goat Science</t>
+          <t>Physiology Dairy Goat</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -1285,7 +1289,7 @@
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>0009-0003-5107-7059</t>
+          <t>0009-0000-3291-0621</t>
         </is>
       </c>
       <c r="K13" s="12" t="n"/>
@@ -1302,12 +1306,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Nur Fajri Muhlish, S. Pt</t>
+          <t>Azisah Nurfadillah, S.Pt</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1324,7 +1328,11 @@
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
       <c r="I14" s="12" t="n"/>
-      <c r="J14" s="12" t="n"/>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>0009-0003-5107-7059</t>
+        </is>
+      </c>
       <c r="K14" s="12" t="n"/>
       <c r="L14" s="12" t="n"/>
       <c r="M14" s="11" t="inlineStr">
@@ -1339,17 +1347,17 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Rara Mufliha, S. Pt., M. Si</t>
+          <t>Nur Fajri Muhlish, S. Pt</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Dairy Science</t>
+          <t>Dairy Goat Science</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -1361,17 +1369,9 @@
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="12" t="n"/>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>0009-0007-1878-6629</t>
-        </is>
-      </c>
+      <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
-      <c r="L15" s="11" t="inlineStr">
-        <is>
-          <t>59161668000</t>
-        </is>
-      </c>
+      <c r="L15" s="12" t="n"/>
       <c r="M15" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1382,18 +1382,46 @@
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="11" t="n"/>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Rara Mufliha, S. Pt., M. Si</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Based at the Dairy Production Laboratory, Faculty of Animal Science, Hasanuddin University in Makassar, Indonesia, our interdisciplinary team combines expertise and experience from various fields. We have established strong research partnerships with institutions in Indonesia, Japan, Malaysia, and Thailand. Our group is actively involved in collaborative research, pursuing grant opportunities, and publishing impactful findings.</t>
+        </is>
+      </c>
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
       <c r="I16" s="12" t="n"/>
-      <c r="J16" s="12" t="n"/>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>0009-0007-1878-6629</t>
+        </is>
+      </c>
       <c r="K16" s="12" t="n"/>
-      <c r="L16" s="12" t="n"/>
-      <c r="M16" s="12" t="n"/>
+      <c r="L16" s="11" t="inlineStr">
+        <is>
+          <t>59161668000</t>
+        </is>
+      </c>
+      <c r="M16" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1582,15 +1610,32 @@
       <c r="L27" s="12" t="n"/>
       <c r="M27" s="12" t="n"/>
     </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="12" t="n"/>
+      <c r="C28" s="12" t="n"/>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="12" t="n"/>
+      <c r="G28" s="12" t="n"/>
+      <c r="H28" s="12" t="n"/>
+      <c r="I28" s="12" t="n"/>
+      <c r="J28" s="12" t="n"/>
+      <c r="K28" s="12" t="n"/>
+      <c r="L28" s="12" t="n"/>
+      <c r="M28" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
